--- a/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
+++ b/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
@@ -507,7 +507,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888 · Fecha de publicación: —</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf · Fecha de publicación: —</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">

--- a/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
+++ b/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
@@ -507,7 +507,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888 · Fecha de publicación: —</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf · Fecha de publicación: 22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -622,12 +622,12 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -680,12 +680,12 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1782,12 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22 de mayo de 2026</t>
         </is>
       </c>
     </row>

--- a/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
+++ b/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
@@ -1214,7 +1214,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2T-23 P</t>
+          <t>2T-23</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
@@ -1446,7 +1446,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2T-24 P</t>
+          <t>2T-24</t>
         </is>
       </c>
       <c r="B21" s="8" t="n">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -1562,7 +1562,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>4T-24 P</t>
+          <t>4T-24</t>
         </is>
       </c>
       <c r="B23" s="8" t="n">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
@@ -1678,7 +1678,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>2T-25 P</t>
+          <t>2T-25</t>
         </is>
       </c>
       <c r="B25" s="8" t="n">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
@@ -1736,7 +1736,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3T-25 P</t>
+          <t>3T-25</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1794,7 +1794,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>4T-25 P</t>
+          <t>4T-25</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>1T-26 P</t>
+          <t>1T-26</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Preliminar</t>
+          <t>Definitivo</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">

--- a/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
+++ b/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PIB trimestral por grandes actividades económicas — Niveles</t>
+          <t>PIB trimestral a precios constantes — Niveles</t>
         </is>
       </c>
     </row>
@@ -522,516 +522,2948 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Nivel PIB</t>
+          <t>PIB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Nivel Primarias</t>
+          <t>Primarias</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Nivel Secundarias</t>
+          <t>Secundarias</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Nivel Terciarias</t>
+          <t>Terciarias</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>1T-18</t>
+          <t>1T-93</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>43101</v>
+        <v>33970</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>24.13728771</v>
+        <v>13.759053956</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.678678138</v>
+        <v>0.469131612</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>7.866374716</v>
+        <v>5.068369546</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>14.313691858</v>
+        <v>7.401189901</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2T-18</t>
+          <t>2T-93</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>43191</v>
+        <v>34060</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>24.605265729</v>
+        <v>13.889145022</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.9273352029999999</v>
+        <v>0.491945188</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7.679579898</v>
+        <v>4.942121692</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>14.753228779</v>
+        <v>7.643696114</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>1T-19</t>
+          <t>3T-93</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>43466</v>
+        <v>34151</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>24.02490635</v>
+        <v>13.862878872</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.6908888129999999</v>
+        <v>0.492499834</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>7.729308418</v>
+        <v>5.1337066</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>14.322078244</v>
+        <v>7.507540588</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2T-19</t>
+          <t>4T-93</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>43556</v>
+        <v>34243</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>24.356643155</v>
+        <v>14.077352767</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.913457081</v>
+        <v>0.529808779</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7.444610529</v>
+        <v>5.15331918</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>14.754773247</v>
+        <v>7.631081987</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>1T-20</t>
+          <t>1T-94</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>43831</v>
+        <v>34335</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>22.072209167</v>
+        <v>14.100080574</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.7305962610000001</v>
+        <v>0.460415889</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>7.169315544</v>
+        <v>5.219093507</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>13.05485882</v>
+        <v>7.563238853000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2T-20</t>
+          <t>2T-94</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>43922</v>
+        <v>34425</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>23.504796547</v>
+        <v>14.655082637</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.9283497589999999</v>
+        <v>0.525072004</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>7.385109781000001</v>
+        <v>5.273651587000001</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>14.047810598</v>
+        <v>7.967044911</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>1T-21</t>
+          <t>3T-94</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>44197</v>
+        <v>34516</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>23.204796817</v>
+        <v>14.488831889</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0.7204531750000001</v>
+        <v>0.456542671</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>7.417983191999999</v>
+        <v>5.385396519</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>13.810362579</v>
+        <v>7.826046468</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2T-21</t>
+          <t>4T-94</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>44287</v>
+        <v>34608</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>23.949712898</v>
+        <v>14.787062247</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.9584566189999999</v>
+        <v>0.537902019</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7.447531382</v>
+        <v>5.345347947</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>14.278012522</v>
+        <v>8.126843855000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>1T-22</t>
+          <t>1T-95</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>44562</v>
+        <v>34700</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>24.289379479</v>
+        <v>14.043942174</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.725282018</v>
+        <v>0.453727054</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>7.805875067</v>
+        <v>5.055171535</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>14.421864812</v>
+        <v>7.665270476</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2T-22</t>
+          <t>2T-95</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>44652</v>
+        <v>34790</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>25.052395779</v>
+        <v>13.28744387</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1.00268571</v>
+        <v>0.493033792</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>7.826990042</v>
+        <v>4.510921396</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>14.899941441</v>
+        <v>7.517247445000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>1T-23</t>
+          <t>3T-95</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>44927</v>
+        <v>34881</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>25.094793141</v>
+        <v>13.41223839</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.7302011269999999</v>
+        <v>0.5010044149999999</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>8.061173693000001</v>
+        <v>4.712732855</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>14.924452582</v>
+        <v>7.471792751</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2T-23</t>
+          <t>4T-95</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>45017</v>
+        <v>34973</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>25.590082607</v>
+        <v>13.85762355</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.9589118000000001</v>
+        <v>0.556326176</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>8.024213122000001</v>
+        <v>4.87195702</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>15.251937656</v>
+        <v>7.703353153</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3T-23 P</t>
+          <t>1T-96</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>45108</v>
-      </c>
-      <c r="C18" s="8" t="n"/>
+        <v>35065</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>14.237650096</v>
+      </c>
       <c r="D18" s="6" t="n">
-        <v>0.7302011269999999</v>
+        <v>0.499745892</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>8.061173693000001</v>
+        <v>5.182979517</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>14.924452582</v>
+        <v>7.700990911</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>4T-23 P</t>
+          <t>2T-96</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>45200</v>
-      </c>
-      <c r="C19" s="4" t="n"/>
+        <v>35156</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>14.340821386</v>
+      </c>
       <c r="D19" s="7" t="n">
-        <v>0.9589118000000001</v>
+        <v>0.514430297</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>8.024213122000001</v>
+        <v>5.121575921</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>15.251937656</v>
+        <v>7.886168973</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>1T-24</t>
+          <t>3T-96</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>45292</v>
+        <v>35247</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>25.475446445</v>
+        <v>14.412887421</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0.783638959</v>
+        <v>0.494418494</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>8.020904247000001</v>
+        <v>5.34633734</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>15.272671829</v>
+        <v>7.806071153</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2T-24</t>
+          <t>4T-96</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>45383</v>
+        <v>35339</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>25.693292983</v>
+        <v>15.005156934</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.930282979</v>
+        <v>0.571737978</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>7.832811484</v>
+        <v>5.533838887</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>15.559800994</v>
+        <v>8.108825022</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3T-24 P</t>
+          <t>1T-97</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>45474</v>
-      </c>
-      <c r="C22" s="8" t="n"/>
+        <v>35431</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>14.809591398</v>
+      </c>
       <c r="D22" s="6" t="n">
-        <v>0.783638959</v>
+        <v>0.501737072</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>8.020904247000001</v>
+        <v>5.474024363</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>15.272671829</v>
+        <v>7.956522789</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>4T-24</t>
+          <t>2T-97</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>45566</v>
-      </c>
-      <c r="C23" s="4" t="n"/>
+        <v>35521</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>15.584335623</v>
+      </c>
       <c r="D23" s="7" t="n">
-        <v>0.930282979</v>
+        <v>0.530032464</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>7.832811484</v>
+        <v>5.6527652</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>15.559800994</v>
+        <v>8.492716331</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>1T-25</t>
+          <t>3T-97</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>45658</v>
+        <v>35612</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>25.422850191</v>
+        <v>15.624252001</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0.777766167</v>
+        <v>0.47566719</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>7.812449734</v>
+        <v>5.910886525</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>15.433943462</v>
+        <v>8.383796178999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2T-25</t>
+          <t>4T-97</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>45748</v>
+        <v>35704</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>26.135644696</v>
+        <v>16.153434161</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>0.9939739719999999</v>
+        <v>0.571826382</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>7.867045889000001</v>
+        <v>5.979006582999999</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>15.877667814</v>
+        <v>8.75383924</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3T-25</t>
+          <t>1T-98</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>45839</v>
-      </c>
-      <c r="C26" s="8" t="n"/>
+        <v>35796</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>16.337214143</v>
+      </c>
       <c r="D26" s="6" t="n">
-        <v>0.777766167</v>
+        <v>0.5257445919999999</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>7.812449734</v>
+        <v>6.157924217000001</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>15.433943462</v>
+        <v>8.666024219000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>4T-25</t>
+          <t>2T-98</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>45931</v>
-      </c>
-      <c r="C27" s="4" t="n"/>
+        <v>35886</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>16.539597626</v>
+      </c>
       <c r="D27" s="7" t="n">
-        <v>0.9939739719999999</v>
+        <v>0.534956447</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>7.867045889000001</v>
+        <v>6.040769573</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>15.877667814</v>
+        <v>8.979968368000002</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>3T-98</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>35977</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>16.552799275</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0.521291101</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>6.272846363</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>8.861628745999999</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>4T-98</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>36069</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>16.587365488</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>0.563942237</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>6.161338306</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>8.994905965999999</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>1T-99</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>36161</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>16.704973282</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.5769999819999999</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>6.266589216</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>8.858739981000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2T-99</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>36251</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>16.929118024</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>0.5266915209999999</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>6.127831179999999</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>9.254905826</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>3T-99</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>36342</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>17.050482211</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.504254554</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>6.416451937</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>9.190243407000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>4T-99</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>36434</v>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>17.151190783</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>0.564425799</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>6.268398904</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>9.412020413</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>1T-00</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>36526</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>17.649705005</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>0.555239686</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>6.611798502</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>9.430285095</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2T-00</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>36617</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>17.862016739</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>0.561193975</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>6.479541566</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>9.777987380999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>3T-00</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>36708</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>18.020884404</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>0.481213062</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>6.836715502000001</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>9.693429777</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>4T-00</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>36800</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>17.714811387</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>0.599293228</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>6.418347265</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>9.804432</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>1T-01</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>36892</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>17.764232953</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>0.5374275080000001</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>6.560661794</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>9.520942301000002</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2T-01</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>36982</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>17.87401934</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0.599395857</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>6.302071073</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>9.847304763</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>3T-01</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>37073</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>17.761059865</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>0.530879234</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>6.588803177</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>9.622904643</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>4T-01</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>37165</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>17.526889778</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>0.643598617</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>6.280006432</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>9.678998801000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>1T-02</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>37257</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>17.079137485</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>0.549329157</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>6.13182851</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>9.306569483999999</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2T-02</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>37347</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>18.01679815</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>0.5891790969999999</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>6.279486019</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>10.004704828</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>3T-02</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>37438</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>17.828003405</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>0.525373627</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>6.506821381</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>9.748196289000001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>4T-02</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>37530</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>17.83446001</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>0.621291567</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>6.383103751</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>9.843188392</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>1T-03</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>37622</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>17.609605878</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>0.56863726</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>6.308267101</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>9.621127448000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2T-03</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>37712</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>18.08266385</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>0.6115773170000001</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>6.33657832</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>9.970370833</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>3T-03</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>37803</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>17.859147302</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>0.54513363</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>6.523452228</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>9.715838193</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>4T-03</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>37895</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>18.045854589</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>0.644565611</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>6.409907565999999</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>9.962912993000002</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>1T-04</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>37987</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>18.185015464</v>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>0.6116243179999999</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>6.55432655</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>9.862624973999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2T-04</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>38078</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>18.770260284</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>0.617553614</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>6.609349025</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>10.335537363</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>3T-04</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>38169</v>
+      </c>
+      <c r="C52" s="6" t="n">
+        <v>18.461379994</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>0.5273778170000001</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>6.742820624</v>
+      </c>
+      <c r="F52" s="6" t="n">
+        <v>10.081493197</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>4T-04</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>38261</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>18.733374373</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>0.67271048</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>6.64864508</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>10.373351197</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>1T-05</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>38353</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>18.271688439</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>0.571083781</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>6.572652178999999</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>9.933962397</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2T-05</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>38443</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>19.218715204</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>0.585893331</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>6.806175828</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>10.570524987</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>3T-05</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>38534</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>18.883270709</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>0.548932541</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>6.850231405000001</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>10.346635468</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>4T-05</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>38626</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>19.343329136</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>0.6483241550000001</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>6.930016648</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>10.683835504</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>1T-06</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>38718</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>19.362570756</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>0.592797559</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>6.987515165</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>10.520692475</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>2T-06</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>38808</v>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>20.116112951</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>0.644430093</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>7.129368379</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>11.022835038</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>3T-06</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>38899</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>19.836008957</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>0.543977743</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>7.27518719</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>10.814056779</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>4T-06</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>38991</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>20.040523076</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>0.714400251</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>7.138741963999999</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>11.045940648</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>1T-07</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>39083</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>19.745597365</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0.618831402</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>7.116558066</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>10.74862036</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>2T-07</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>39173</v>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>20.509471918</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>0.680502853</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>7.227258756</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>11.283820681</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>3T-07</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>39264</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>20.266835203</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>0.572297676</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>7.306670858</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>11.177416519</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>4T-07</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>39356</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>20.482204665</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>0.732924061</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>7.206855661000001</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>11.428227271</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>1T-08</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>39448</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>19.90292179</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>0.609458186</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>7.088503908</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>10.904087123</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>2T-08</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>39539</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>20.99850391</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>0.698691862</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>7.290207761</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>11.617818104</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>3T-08</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>39630</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>20.495872627</v>
+      </c>
+      <c r="D68" s="6" t="n">
+        <v>0.563853185</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>7.216495651</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>11.457823121</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>4T-08</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>39722</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>20.370948404</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>0.753298764</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>7.019775964</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>11.43525489</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>1T-09</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>39814</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>18.537259148</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0.599965766</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>6.383401005</v>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>10.409714859</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2T-09</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>39904</v>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>18.827563207</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>0.6818991339999999</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>6.420353509</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>10.587429028</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>3T-09</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>39995</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>19.292209618</v>
+      </c>
+      <c r="D72" s="6" t="n">
+        <v>0.55436553</v>
+      </c>
+      <c r="E72" s="6" t="n">
+        <v>6.684243826</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>10.935866207</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>4T-09</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>40087</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>19.963698743</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>0.7160679679999999</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>6.810224411</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>11.341950474</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>1T-10</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>40179</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>19.371870871</v>
+      </c>
+      <c r="D74" s="6" t="n">
+        <v>0.586514444</v>
+      </c>
+      <c r="E74" s="6" t="n">
+        <v>6.696977626</v>
+      </c>
+      <c r="F74" s="6" t="n">
+        <v>10.956604462</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>2T-10</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>40269</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>20.180561282</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>0.723013451</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>6.892643779</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>11.379540882</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>3T-10</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>40360</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>20.200797992</v>
+      </c>
+      <c r="D76" s="6" t="n">
+        <v>0.5882830579999999</v>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>6.983534678000001</v>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>11.527917746</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>4T-10</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>40452</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>20.676573452</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>0.7162629540000001</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>6.961241719999999</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>11.945987766</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>1T-11</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>40544</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>20.091352133</v>
+      </c>
+      <c r="D78" s="6" t="n">
+        <v>0.591331127</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>6.837462284</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>11.518519394</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2T-11</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>40634</v>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>20.682934142</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>0.640002259</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>7.041134400000001</v>
+      </c>
+      <c r="F79" s="7" t="n">
+        <v>11.819730299</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>3T-11</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>40725</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>20.950181653</v>
+      </c>
+      <c r="D80" s="6" t="n">
+        <v>0.5898025699999999</v>
+      </c>
+      <c r="E80" s="6" t="n">
+        <v>7.203286747000001</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>12.054645365</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>4T-11</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>40817</v>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>21.475374344</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>0.729678032</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>7.318706614</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>12.354200882</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>1T-12</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>40909</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>21.083780274</v>
+      </c>
+      <c r="D82" s="6" t="n">
+        <v>0.613060893</v>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>7.22774077</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>12.062944807</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2T-12</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>21.522112939</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>0.7191249599999999</v>
+      </c>
+      <c r="E83" s="7" t="n">
+        <v>7.360415271</v>
+      </c>
+      <c r="F83" s="7" t="n">
+        <v>12.249460429</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>3T-12</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>41091</v>
+      </c>
+      <c r="C84" s="6" t="n">
+        <v>21.479008345</v>
+      </c>
+      <c r="D84" s="6" t="n">
+        <v>0.592829841</v>
+      </c>
+      <c r="E84" s="6" t="n">
+        <v>7.460822202999999</v>
+      </c>
+      <c r="F84" s="6" t="n">
+        <v>12.307326348</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>4T-12</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>41183</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>22.07120647</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>0.780235075</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>7.364743136</v>
+      </c>
+      <c r="F85" s="7" t="n">
+        <v>12.854393124</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>1T-13</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>41275</v>
+      </c>
+      <c r="C86" s="6" t="n">
+        <v>21.025801061</v>
+      </c>
+      <c r="D86" s="6" t="n">
+        <v>0.619948865</v>
+      </c>
+      <c r="E86" s="6" t="n">
+        <v>7.102917541</v>
+      </c>
+      <c r="F86" s="6" t="n">
+        <v>12.150217498</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2T-13</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>41365</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>21.893508352</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>0.752123102</v>
+      </c>
+      <c r="E87" s="7" t="n">
+        <v>7.366725400999999</v>
+      </c>
+      <c r="F87" s="7" t="n">
+        <v>12.581930176</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>3T-13</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>41456</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>21.702816349</v>
+      </c>
+      <c r="D88" s="6" t="n">
+        <v>0.6112775579999999</v>
+      </c>
+      <c r="E88" s="6" t="n">
+        <v>7.380939988</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>12.596331654</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>4T-13</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>41548</v>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>22.268119789</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>0.8034688299999999</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>7.408177765</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>12.992728474</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>1T-14</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>41640</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>21.547782441</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>0.64834107</v>
+      </c>
+      <c r="E90" s="6" t="n">
+        <v>7.287254571</v>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>12.429874668</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2T-14</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>41730</v>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>22.320155991</v>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>0.768627492</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>7.569038085</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>12.772327006</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>3T-14</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>41821</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>22.258188342</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>0.643268097</v>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>7.593723666</v>
+      </c>
+      <c r="F92" s="6" t="n">
+        <v>12.891190056</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>4T-14</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>41913</v>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>22.939645045</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>0.81451294</v>
+      </c>
+      <c r="E93" s="7" t="n">
+        <v>7.6591607</v>
+      </c>
+      <c r="F93" s="7" t="n">
+        <v>13.353810132</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>1T-15</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>42005</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>22.169554364</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>0.682708429</v>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>7.43677541</v>
+      </c>
+      <c r="F94" s="6" t="n">
+        <v>12.828790068</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2T-15</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>42095</v>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>22.843017522</v>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>0.762292168</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>7.620335485</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>13.192282882</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>3T-15</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>42186</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>23.0117458</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>0.633891785</v>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>7.851923139</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>13.321234659</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>4T-15</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>42278</v>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>23.448299342</v>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>0.8491228810000001</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>7.748226577</v>
+      </c>
+      <c r="F97" s="7" t="n">
+        <v>13.661991741</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>1T-16</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>42370</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>22.537031335</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>0.675450518</v>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>7.519199238</v>
+      </c>
+      <c r="F98" s="6" t="n">
+        <v>13.089582885</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2T-16</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>42461</v>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>23.35995577</v>
+      </c>
+      <c r="D99" s="7" t="n">
+        <v>0.783292895</v>
+      </c>
+      <c r="E99" s="7" t="n">
+        <v>7.741594476</v>
+      </c>
+      <c r="F99" s="7" t="n">
+        <v>13.535631125</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>3T-16</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>42552</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>23.214541358</v>
+      </c>
+      <c r="D100" s="6" t="n">
+        <v>0.675022005</v>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>7.736587845</v>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>13.571616482</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>4T-16</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>42644</v>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>23.982434514</v>
+      </c>
+      <c r="D101" s="7" t="n">
+        <v>0.879613121</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>7.747450987</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>14.146147656</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>1T-17</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>42736</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>23.306068739</v>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>0.713904756</v>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>7.696752221</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>13.595771827</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2T-17</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>42826</v>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>23.710325711</v>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>0.804164686</v>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>7.735461008000001</v>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>13.834995631</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>3T-17</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>42917</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>23.491266413</v>
+      </c>
+      <c r="D104" s="6" t="n">
+        <v>0.6770095429999999</v>
+      </c>
+      <c r="E104" s="6" t="n">
+        <v>7.762752647</v>
+      </c>
+      <c r="F104" s="6" t="n">
+        <v>13.806778422</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>4T-17</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>43009</v>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>24.32876839</v>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>0.9167705350000001</v>
+      </c>
+      <c r="E105" s="7" t="n">
+        <v>7.742366961</v>
+      </c>
+      <c r="F105" s="7" t="n">
+        <v>14.459683456</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>1T-18</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>43101</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>23.568391999</v>
+      </c>
+      <c r="D106" s="6" t="n">
+        <v>0.74623751</v>
+      </c>
+      <c r="E106" s="6" t="n">
+        <v>7.595975489</v>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v>13.899895284</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2T-18</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>43191</v>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>24.395736063</v>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>0.836129224</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>7.846628792000001</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>14.350827278</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>3T-18</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>43282</v>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>24.13728771</v>
+      </c>
+      <c r="D108" s="6" t="n">
+        <v>0.678678138</v>
+      </c>
+      <c r="E108" s="6" t="n">
+        <v>7.866374716</v>
+      </c>
+      <c r="F108" s="6" t="n">
+        <v>14.313691858</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>4T-18</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>43374</v>
+      </c>
+      <c r="C109" s="7" t="n">
+        <v>24.605265729</v>
+      </c>
+      <c r="D109" s="7" t="n">
+        <v>0.9273352029999999</v>
+      </c>
+      <c r="E109" s="7" t="n">
+        <v>7.679579898</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>14.753228779</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>23.790581652</v>
+      </c>
+      <c r="D110" s="6" t="n">
+        <v>0.762358255</v>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v>7.585247998</v>
+      </c>
+      <c r="F110" s="6" t="n">
+        <v>14.098986406</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2T-19</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>43556</v>
+      </c>
+      <c r="C111" s="7" t="n">
+        <v>24.154792378</v>
+      </c>
+      <c r="D111" s="7" t="n">
+        <v>0.831203432</v>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>7.689870355999999</v>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>14.270949004</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>3T-19</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>43647</v>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>24.02490635</v>
+      </c>
+      <c r="D112" s="6" t="n">
+        <v>0.6908888129999999</v>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v>7.729308418</v>
+      </c>
+      <c r="F112" s="6" t="n">
+        <v>14.322078244</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>4T-19</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>43739</v>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>24.356643155</v>
+      </c>
+      <c r="D113" s="7" t="n">
+        <v>0.913457081</v>
+      </c>
+      <c r="E113" s="7" t="n">
+        <v>7.444610529</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>14.754773247</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>23.449993643</v>
+      </c>
+      <c r="D114" s="6" t="n">
+        <v>0.753610892</v>
+      </c>
+      <c r="E114" s="6" t="n">
+        <v>7.388698882</v>
+      </c>
+      <c r="F114" s="6" t="n">
+        <v>14.013025696</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2T-20</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>43922</v>
+      </c>
+      <c r="C115" s="7" t="n">
+        <v>19.252739685</v>
+      </c>
+      <c r="D115" s="7" t="n">
+        <v>0.821162608</v>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>5.814815401</v>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>11.664084703</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>3T-20</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>44013</v>
+      </c>
+      <c r="C116" s="6" t="n">
+        <v>22.072209167</v>
+      </c>
+      <c r="D116" s="6" t="n">
+        <v>0.7305962610000001</v>
+      </c>
+      <c r="E116" s="6" t="n">
+        <v>7.169315544</v>
+      </c>
+      <c r="F116" s="6" t="n">
+        <v>13.05485882</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>4T-20</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>44105</v>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>23.504796547</v>
+      </c>
+      <c r="D117" s="7" t="n">
+        <v>0.9283497589999999</v>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>7.385109781000001</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>14.047810598</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C118" s="6" t="n">
+        <v>22.841359685</v>
+      </c>
+      <c r="D118" s="6" t="n">
+        <v>0.757806238</v>
+      </c>
+      <c r="E118" s="6" t="n">
+        <v>7.266162011</v>
+      </c>
+      <c r="F118" s="6" t="n">
+        <v>13.609045197</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2T-21</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>44287</v>
+      </c>
+      <c r="C119" s="7" t="n">
+        <v>23.623455056</v>
+      </c>
+      <c r="D119" s="7" t="n">
+        <v>0.872119144</v>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>7.39723624</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>14.063214857</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>3T-21</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="C120" s="6" t="n">
+        <v>23.204796817</v>
+      </c>
+      <c r="D120" s="6" t="n">
+        <v>0.7204531750000001</v>
+      </c>
+      <c r="E120" s="6" t="n">
+        <v>7.417983191999999</v>
+      </c>
+      <c r="F120" s="6" t="n">
+        <v>13.810362579</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>4T-21</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C121" s="7" t="n">
+        <v>23.949712898</v>
+      </c>
+      <c r="D121" s="7" t="n">
+        <v>0.9584566189999999</v>
+      </c>
+      <c r="E121" s="7" t="n">
+        <v>7.447531382</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>14.278012522</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C122" s="6" t="n">
+        <v>23.440574466</v>
+      </c>
+      <c r="D122" s="6" t="n">
+        <v>0.76330939</v>
+      </c>
+      <c r="E122" s="6" t="n">
+        <v>7.571406381</v>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v>13.81754203</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2T-22</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>44652</v>
+      </c>
+      <c r="C123" s="7" t="n">
+        <v>24.310024252</v>
+      </c>
+      <c r="D123" s="7" t="n">
+        <v>0.869367643</v>
+      </c>
+      <c r="E123" s="7" t="n">
+        <v>7.728548662</v>
+      </c>
+      <c r="F123" s="7" t="n">
+        <v>14.325766844</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>3T-22</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="C124" s="6" t="n">
+        <v>24.289379479</v>
+      </c>
+      <c r="D124" s="6" t="n">
+        <v>0.725282018</v>
+      </c>
+      <c r="E124" s="6" t="n">
+        <v>7.805875067</v>
+      </c>
+      <c r="F124" s="6" t="n">
+        <v>14.421864812</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>4T-22</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>44835</v>
+      </c>
+      <c r="C125" s="7" t="n">
+        <v>25.052395779</v>
+      </c>
+      <c r="D125" s="7" t="n">
+        <v>1.00268571</v>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>7.826990042</v>
+      </c>
+      <c r="F125" s="7" t="n">
+        <v>14.899941441</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C126" s="6" t="n">
+        <v>24.330982536</v>
+      </c>
+      <c r="D126" s="6" t="n">
+        <v>0.767720639</v>
+      </c>
+      <c r="E126" s="6" t="n">
+        <v>7.800352717</v>
+      </c>
+      <c r="F126" s="6" t="n">
+        <v>14.382920096</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>2T-23</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>45017</v>
+      </c>
+      <c r="C127" s="7" t="n">
+        <v>25.10826825</v>
+      </c>
+      <c r="D127" s="7" t="n">
+        <v>0.866388559</v>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>7.964375032</v>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>14.833956646</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>3T-23</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="C128" s="6" t="n">
+        <v>25.094793141</v>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>0.7302011269999999</v>
+      </c>
+      <c r="E128" s="6" t="n">
+        <v>8.061173693000001</v>
+      </c>
+      <c r="F128" s="6" t="n">
+        <v>14.924452582</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>4T-23</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>45200</v>
+      </c>
+      <c r="C129" s="7" t="n">
+        <v>25.590082607</v>
+      </c>
+      <c r="D129" s="7" t="n">
+        <v>0.9589118000000001</v>
+      </c>
+      <c r="E129" s="7" t="n">
+        <v>8.024213122000001</v>
+      </c>
+      <c r="F129" s="7" t="n">
+        <v>15.251937656</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C130" s="6" t="n">
+        <v>24.761655524</v>
+      </c>
+      <c r="D130" s="6" t="n">
+        <v>0.7633377020000001</v>
+      </c>
+      <c r="E130" s="6" t="n">
+        <v>7.795986431</v>
+      </c>
+      <c r="F130" s="6" t="n">
+        <v>14.792896131</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>2T-24</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>45383</v>
+      </c>
+      <c r="C131" s="7" t="n">
+        <v>25.655479047</v>
+      </c>
+      <c r="D131" s="7" t="n">
+        <v>0.866987775</v>
+      </c>
+      <c r="E131" s="7" t="n">
+        <v>8.011179289999999</v>
+      </c>
+      <c r="F131" s="7" t="n">
+        <v>15.297892114</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>3T-24</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="C132" s="6" t="n">
+        <v>25.475446445</v>
+      </c>
+      <c r="D132" s="6" t="n">
+        <v>0.783638959</v>
+      </c>
+      <c r="E132" s="6" t="n">
+        <v>8.020904247000001</v>
+      </c>
+      <c r="F132" s="6" t="n">
+        <v>15.272671829</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>4T-24</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C133" s="7" t="n">
+        <v>25.693292983</v>
+      </c>
+      <c r="D133" s="7" t="n">
+        <v>0.930282979</v>
+      </c>
+      <c r="E133" s="7" t="n">
+        <v>7.832811484</v>
+      </c>
+      <c r="F133" s="7" t="n">
+        <v>15.559800994</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C134" s="6" t="n">
+        <v>24.913610281</v>
+      </c>
+      <c r="D134" s="6" t="n">
+        <v>0.794706899</v>
+      </c>
+      <c r="E134" s="6" t="n">
+        <v>7.715395565000001</v>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v>14.984362696</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>2T-25</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C135" s="7" t="n">
+        <v>25.618678767</v>
+      </c>
+      <c r="D135" s="7" t="n">
+        <v>0.856980339</v>
+      </c>
+      <c r="E135" s="7" t="n">
+        <v>7.88892488</v>
+      </c>
+      <c r="F135" s="7" t="n">
+        <v>15.388336602</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>3T-25</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C136" s="6" t="n">
+        <v>25.422850191</v>
+      </c>
+      <c r="D136" s="6" t="n">
+        <v>0.777766167</v>
+      </c>
+      <c r="E136" s="6" t="n">
+        <v>7.812449734</v>
+      </c>
+      <c r="F136" s="6" t="n">
+        <v>15.433943462</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>4T-25</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C137" s="7" t="n">
+        <v>26.135644696</v>
+      </c>
+      <c r="D137" s="7" t="n">
+        <v>0.9939739719999999</v>
+      </c>
+      <c r="E137" s="7" t="n">
+        <v>7.867045889000001</v>
+      </c>
+      <c r="F137" s="7" t="n">
+        <v>15.877667814</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
           <t>1T-26</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B138" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C138" s="6" t="n">
         <v>24.973976071</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D138" s="6" t="n">
         <v>0.797675498</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E138" s="6" t="n">
         <v>7.621773386</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F138" s="6" t="n">
         <v>15.134329955</v>
       </c>
     </row>
@@ -1051,7 +3483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1069,7 +3501,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PIB trimestral por grandes actividades económicas — Variaciones</t>
+          <t>PIB trimestral a precios constantes — Variaciones</t>
         </is>
       </c>
     </row>
@@ -1142,11 +3574,11 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>1T-18</t>
+          <t>1T-93</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>43101</v>
+        <v>33970</v>
       </c>
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="n"/>
@@ -1160,494 +3592,4464 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2T-18</t>
+          <t>2T-93</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>43191</v>
-      </c>
-      <c r="C7" s="4" t="n"/>
+        <v>34060</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>0.009455</v>
+      </c>
       <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
+      <c r="E7" s="9" t="n">
+        <v>0.048629</v>
+      </c>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="G7" s="9" t="n">
+        <v>-0.024909</v>
+      </c>
       <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
+      <c r="I7" s="9" t="n">
+        <v>0.032766</v>
+      </c>
       <c r="J7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>1T-19</t>
+          <t>3T-93</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>43466</v>
-      </c>
-      <c r="C8" s="8" t="n"/>
+        <v>34151</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>-0.001891</v>
+      </c>
       <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
+      <c r="E8" s="10" t="n">
+        <v>0.001127</v>
+      </c>
       <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
+      <c r="G8" s="10" t="n">
+        <v>0.038766</v>
+      </c>
       <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
+      <c r="I8" s="10" t="n">
+        <v>-0.017813</v>
+      </c>
       <c r="J8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>2T-19</t>
+          <t>4T-93</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>43556</v>
-      </c>
-      <c r="C9" s="4" t="n"/>
+        <v>34243</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>0.015471</v>
+      </c>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
+      <c r="E9" s="9" t="n">
+        <v>0.075754</v>
+      </c>
       <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="G9" s="9" t="n">
+        <v>0.00382</v>
+      </c>
       <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
+      <c r="I9" s="9" t="n">
+        <v>0.016456</v>
+      </c>
       <c r="J9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>1T-20</t>
+          <t>1T-94</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
+        <v>34335</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>0.001614</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>0.024786</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>-0.130977</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>-0.018578</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0.012763</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>0.029738</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>-0.00889</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>0.021895</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2T-20</t>
+          <t>2T-94</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>43922</v>
-      </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
+        <v>34425</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0.039362</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.055146</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.14043</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.067338</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>0.010454</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>0.067083</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0.053391</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.042303</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>1T-21</t>
+          <t>3T-94</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>44197</v>
-      </c>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
+        <v>34516</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>-0.011344</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0.045153</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.130514</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>-0.073009</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0.021189</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>0.049027</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>-0.017698</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>0.042425</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2T-21</t>
+          <t>4T-94</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>44287</v>
-      </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
+        <v>34608</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>0.020583</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.050415</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>0.178208</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>0.015276</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>-0.007437</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>0.037263</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>0.038435</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.064966</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>1T-22</t>
+          <t>1T-95</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>44562</v>
-      </c>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n"/>
+        <v>34700</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>-0.050255</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>-0.003981</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.156488</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>-0.014528</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>-0.054286</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>-0.031408</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>-0.056796</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>0.01349</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2T-22</t>
+          <t>2T-95</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>44652</v>
-      </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
+        <v>34790</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>-0.053867</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>-0.093322</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.086631</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>-0.061017</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>-0.107662</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>-0.14463</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>-0.019311</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>-0.056457</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>1T-23</t>
+          <t>3T-95</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>44927</v>
-      </c>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
+        <v>34881</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>0.009391999999999999</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>-0.074305</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.016166</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>0.097388</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>0.044738</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>-0.124905</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>-0.006047</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>-0.045266</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2T-23</t>
+          <t>4T-95</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>45017</v>
-      </c>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
+        <v>34973</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>0.033207</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>-0.06285499999999999</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>0.110422</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>0.034252</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>0.033786</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>-0.088561</v>
+      </c>
       <c r="I17" s="9" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J17" s="4" t="n"/>
+        <v>0.030991</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>-0.05211</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>3T-23 P</t>
+          <t>1T-96</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>45108</v>
-      </c>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
+        <v>35065</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>0.027424</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0.013793</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.101703</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>0.101424</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>0.06383900000000001</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>0.025283</v>
+      </c>
       <c r="I18" s="10" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J18" s="8" t="n"/>
+        <v>-0.000307</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>0.00466</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>4T-23 P</t>
+          <t>2T-96</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>45200</v>
-      </c>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
+        <v>35156</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>0.007246</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.079276</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0.029384</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>0.043398</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>-0.011847</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>0.135372</v>
+      </c>
       <c r="I19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n"/>
+        <v>0.024046</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.049077</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>1T-24</t>
+          <t>3T-96</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>45292</v>
-      </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
+        <v>35247</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>0.005025</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0.07460700000000001</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-0.038901</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>-0.013145</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>0.043885</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>0.134445</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>-0.010157</v>
+      </c>
+      <c r="J20" s="10" t="n">
+        <v>0.044739</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>2T-24</t>
+          <t>4T-96</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>45383</v>
-      </c>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
+        <v>35339</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>0.041093</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.08280899999999999</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0.156385</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>0.027703</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>0.035071</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>0.135855</v>
+      </c>
       <c r="I21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="n"/>
+        <v>0.038784</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.052636</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>3T-24 P</t>
+          <t>1T-97</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>45474</v>
-      </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
+        <v>35431</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>-0.013033</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>0.040171</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.122435</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>0.003984</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>-0.010809</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>0.056154</v>
+      </c>
       <c r="I22" s="10" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="J22" s="8" t="n"/>
+        <v>-0.018782</v>
+      </c>
+      <c r="J22" s="10" t="n">
+        <v>0.033182</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>4T-24</t>
+          <t>2T-97</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>45566</v>
-      </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
+        <v>35521</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>0.052314</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.086712</v>
+      </c>
       <c r="E23" s="9" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.056395</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>-0.041</v>
+        <v>0.030329</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.015</v>
+        <v>0.032653</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>-0.02</v>
+        <v>0.103716</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>0.002</v>
+        <v>0.06739000000000001</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.021</v>
+        <v>0.076913</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>1T-25</t>
+          <t>3T-97</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>45658</v>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+        <v>35612</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>0.002561</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0.084047</v>
+      </c>
       <c r="E24" s="10" t="n">
-        <v>0.078</v>
+        <v>-0.10257</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>0.067</v>
+        <v>-0.037926</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>-0.001</v>
+        <v>0.045663</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>-0.013</v>
+        <v>0.105596</v>
       </c>
       <c r="I24" s="10" t="n">
-        <v>-0.001</v>
+        <v>-0.012825</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>0.011</v>
+        <v>0.07401000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>2T-25</t>
+          <t>4T-97</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>45748</v>
+        <v>35704</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>0.006</v>
+        <v>0.033869</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.012</v>
+        <v>0.076526</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>-0.024</v>
+        <v>0.202156</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0.026</v>
+        <v>0.000155</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0.007</v>
+        <v>0.011525</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>-0.003</v>
+        <v>0.080445</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0.008</v>
+        <v>0.044138</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.018</v>
+        <v>0.079545</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>3T-25</t>
+          <t>1T-98</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>45839</v>
+        <v>35796</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>-0.003</v>
+        <v>0.011377</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>-0.002</v>
+        <v>0.103151</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>0.035</v>
+        <v>-0.08058700000000001</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>0.029</v>
+        <v>0.047849</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>-0.015</v>
+        <v>0.029924</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>-0.027</v>
+        <v>0.124935</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>0.002</v>
+        <v>-0.010032</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>0.01</v>
+        <v>0.089172</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>4T-25</t>
+          <t>2T-98</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>45931</v>
+        <v>35886</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.012388</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.018</v>
+        <v>0.061296</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>-0.014</v>
+        <v>0.017522</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.078</v>
+        <v>0.00929</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.019025</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.003</v>
+        <v>0.06864000000000001</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.036227</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.021</v>
+        <v>0.057373</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>3T-98</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>35977</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>0.000798</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>0.05943</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>-0.025545</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>0.095916</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>0.038418</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>0.061236</v>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>-0.013178</v>
+      </c>
+      <c r="J28" s="10" t="n">
+        <v>0.056995</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>4T-98</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>36069</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>0.002088</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.026863</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0.081818</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>-0.013788</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>-0.017776</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>0.030495</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>0.01504</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.027538</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>1T-99</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>36161</v>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>0.00709</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0.022511</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.023154</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>0.09749099999999999</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>0.017082</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>0.017646</v>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>-0.015138</v>
+      </c>
+      <c r="J30" s="10" t="n">
+        <v>0.022238</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>2T-99</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>36251</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>0.013418</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0.023551</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>-0.08719</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>-0.01545</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>-0.022143</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>0.014412</v>
+      </c>
+      <c r="I31" s="9" t="n">
+        <v>0.04472</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>0.030617</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>3T-99</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>36342</v>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>0.007169</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>0.030066</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.0426</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>-0.032681</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>0.0471</v>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>0.022893</v>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>-0.006987</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>0.037083</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>4T-99</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>36434</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>0.005906</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0.033991</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0.119327</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>0.000857</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>-0.023074</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>0.017376</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>0.024132</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0.046372</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>1T-00</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>36526</v>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>0.029066</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>0.056554</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>-0.016275</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>-0.037713</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>0.054783</v>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>0.055087</v>
+      </c>
+      <c r="I34" s="10" t="n">
+        <v>0.001941</v>
+      </c>
+      <c r="J34" s="10" t="n">
+        <v>0.06451800000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>2T-00</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>36617</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>0.012029</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.055106</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0.010724</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>0.065508</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>-0.020003</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>0.057396</v>
+      </c>
+      <c r="I35" s="9" t="n">
+        <v>0.036871</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.056519</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>3T-00</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>36708</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>0.008894000000000001</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>0.056913</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.142519</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>-0.045694</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>0.055123</v>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>0.065498</v>
+      </c>
+      <c r="I36" s="10" t="n">
+        <v>-0.008647999999999999</v>
+      </c>
+      <c r="J36" s="10" t="n">
+        <v>0.054752</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>4T-00</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>36800</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>-0.016984</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0.032862</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0.24538</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>0.061775</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>-0.061194</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>0.023921</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>0.011451</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>0.041693</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>1T-01</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>36892</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>0.00279</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>0.006489</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>-0.103231</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>-0.03208</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>0.022173</v>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>-0.007734</v>
+      </c>
+      <c r="I38" s="10" t="n">
+        <v>-0.028914</v>
+      </c>
+      <c r="J38" s="10" t="n">
+        <v>0.009613</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2T-01</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>36982</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>0.00618</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0.000672</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0.115306</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>0.06807299999999999</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>-0.039415</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>-0.027389</v>
+      </c>
+      <c r="I39" s="9" t="n">
+        <v>0.034278</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.007089</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>3T-01</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>37073</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>-0.00632</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>-0.014418</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>-0.114309</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>0.10321</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>0.045498</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>-0.036262</v>
+      </c>
+      <c r="I40" s="10" t="n">
+        <v>-0.022788</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>-0.007276</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>4T-01</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>37165</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>-0.013184</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>-0.010608</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0.212326</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>0.07392899999999999</v>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>-0.046867</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>-0.021554</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>0.005829</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>-0.012794</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>1T-02</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>37257</v>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>-0.025547</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>-0.038566</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.146472</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>0.022146</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>-0.023595</v>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v>-0.06536400000000001</v>
+      </c>
+      <c r="I42" s="10" t="n">
+        <v>-0.038478</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>-0.022516</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2T-02</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>37347</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>0.054901</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0.007988</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0.072543</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>-0.017045</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>0.024081</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>-0.003584</v>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>0.075015</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0.015984</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>3T-02</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>37438</v>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>-0.010479</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>0.003769</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>-0.108296</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>-0.010371</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>0.036203</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>-0.012443</v>
+      </c>
+      <c r="I44" s="10" t="n">
+        <v>-0.025639</v>
+      </c>
+      <c r="J44" s="10" t="n">
+        <v>0.01302</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>4T-02</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>37530</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>0.000362</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0.017548</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>0.182571</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>-0.03466</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>-0.019014</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>0.016417</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>0.009745</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0.016963</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>1T-03</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>37622</v>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>-0.012608</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>0.031059</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.08475000000000001</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>0.035149</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>-0.011724</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>0.028774</v>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>-0.02256</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>0.0338</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2T-03</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>37712</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>0.026864</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.003656</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0.075514</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>0.038016</v>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>0.004488</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>0.009091999999999999</v>
+      </c>
+      <c r="I47" s="9" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>-0.003432</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>3T-03</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>37803</v>
+      </c>
+      <c r="C48" s="10" t="n">
+        <v>-0.012361</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <v>0.001747</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.108643</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>0.037611</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>0.029491</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>0.002556</v>
+      </c>
+      <c r="I48" s="10" t="n">
+        <v>-0.025529</v>
+      </c>
+      <c r="J48" s="10" t="n">
+        <v>-0.003319</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>4T-03</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>37895</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>0.010454</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.011853</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0.182399</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>0.037461</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>-0.017406</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>0.004199</v>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>0.02543</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.012163</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>1T-04</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>37987</v>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>0.007712</v>
+      </c>
+      <c r="D50" s="10" t="n">
+        <v>0.032676</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>-0.051106</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>0.075597</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>0.022531</v>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>0.039006</v>
+      </c>
+      <c r="I50" s="10" t="n">
+        <v>-0.010066</v>
+      </c>
+      <c r="J50" s="10" t="n">
+        <v>0.025101</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2T-04</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>38078</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>0.032183</v>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>0.038025</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>0.009693999999999999</v>
+      </c>
+      <c r="F51" s="9" t="n">
+        <v>0.009771999999999999</v>
+      </c>
+      <c r="G51" s="9" t="n">
+        <v>0.008395</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>0.043047</v>
+      </c>
+      <c r="I51" s="9" t="n">
+        <v>0.04795</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>0.036625</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>3T-04</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>38169</v>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>-0.016456</v>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>0.033721</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.146021</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>-0.032571</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>0.020194</v>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>0.033628</v>
+      </c>
+      <c r="I52" s="10" t="n">
+        <v>-0.02458</v>
+      </c>
+      <c r="J52" s="10" t="n">
+        <v>0.037635</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>4T-04</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>38261</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>0.014733</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>0.038098</v>
+      </c>
+      <c r="E53" s="9" t="n">
+        <v>0.275576</v>
+      </c>
+      <c r="F53" s="9" t="n">
+        <v>0.043665</v>
+      </c>
+      <c r="G53" s="9" t="n">
+        <v>-0.013967</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>0.037245</v>
+      </c>
+      <c r="I53" s="9" t="n">
+        <v>0.02895</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>0.041197</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>1T-05</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>38353</v>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>-0.024645</v>
+      </c>
+      <c r="D54" s="10" t="n">
+        <v>0.004766</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.15107</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>-0.06628299999999999</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>-0.01143</v>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>0.002796</v>
+      </c>
+      <c r="I54" s="10" t="n">
+        <v>-0.042357</v>
+      </c>
+      <c r="J54" s="10" t="n">
+        <v>0.007233</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2T-05</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>38443</v>
+      </c>
+      <c r="C55" s="9" t="n">
+        <v>0.05183</v>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>0.023892</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>0.025932</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>-0.051267</v>
+      </c>
+      <c r="G55" s="9" t="n">
+        <v>0.03553</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>0.02978</v>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>0.064079</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0.022736</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>3T-05</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>38534</v>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>-0.017454</v>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>0.022853</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>-0.063085</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>0.040872</v>
+      </c>
+      <c r="G56" s="10" t="n">
+        <v>0.006473</v>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>0.01593</v>
+      </c>
+      <c r="I56" s="10" t="n">
+        <v>-0.021181</v>
+      </c>
+      <c r="J56" s="10" t="n">
+        <v>0.0263</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>4T-05</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>38626</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>0.024363</v>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>0.03256</v>
+      </c>
+      <c r="E57" s="9" t="n">
+        <v>0.181063</v>
+      </c>
+      <c r="F57" s="9" t="n">
+        <v>-0.036251</v>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>0.011647</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>0.04232</v>
+      </c>
+      <c r="I57" s="9" t="n">
+        <v>0.03259</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>0.029931</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>1T-06</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>38718</v>
+      </c>
+      <c r="C58" s="10" t="n">
+        <v>0.000995</v>
+      </c>
+      <c r="D58" s="10" t="n">
+        <v>0.059703</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.085646</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>0.038022</v>
+      </c>
+      <c r="G58" s="10" t="n">
+        <v>0.008297000000000001</v>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>0.06312</v>
+      </c>
+      <c r="I58" s="10" t="n">
+        <v>-0.01527</v>
+      </c>
+      <c r="J58" s="10" t="n">
+        <v>0.059063</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>2T-06</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>38808</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>0.038917</v>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>0.046694</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="F59" s="9" t="n">
+        <v>0.09991</v>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>0.020301</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>0.047485</v>
+      </c>
+      <c r="I59" s="9" t="n">
+        <v>0.047729</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0.04279</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>3T-06</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>38899</v>
+      </c>
+      <c r="C60" s="10" t="n">
+        <v>-0.013924</v>
+      </c>
+      <c r="D60" s="10" t="n">
+        <v>0.050454</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.155878</v>
+      </c>
+      <c r="F60" s="10" t="n">
+        <v>-0.009025999999999999</v>
+      </c>
+      <c r="G60" s="10" t="n">
+        <v>0.020453</v>
+      </c>
+      <c r="H60" s="10" t="n">
+        <v>0.062035</v>
+      </c>
+      <c r="I60" s="10" t="n">
+        <v>-0.018941</v>
+      </c>
+      <c r="J60" s="10" t="n">
+        <v>0.045176</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>4T-06</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>38991</v>
+      </c>
+      <c r="C61" s="9" t="n">
+        <v>0.01031</v>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>0.036043</v>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>0.313289</v>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>0.101918</v>
+      </c>
+      <c r="G61" s="9" t="n">
+        <v>-0.018755</v>
+      </c>
+      <c r="H61" s="9" t="n">
+        <v>0.030119</v>
+      </c>
+      <c r="I61" s="9" t="n">
+        <v>0.021443</v>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>0.033893</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>1T-07</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>39083</v>
+      </c>
+      <c r="C62" s="10" t="n">
+        <v>-0.014716</v>
+      </c>
+      <c r="D62" s="10" t="n">
+        <v>0.019782</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.133775</v>
+      </c>
+      <c r="F62" s="10" t="n">
+        <v>0.043917</v>
+      </c>
+      <c r="G62" s="10" t="n">
+        <v>-0.003108</v>
+      </c>
+      <c r="H62" s="10" t="n">
+        <v>0.018468</v>
+      </c>
+      <c r="I62" s="10" t="n">
+        <v>-0.026917</v>
+      </c>
+      <c r="J62" s="10" t="n">
+        <v>0.021665</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>2T-07</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>39173</v>
+      </c>
+      <c r="C63" s="9" t="n">
+        <v>0.038686</v>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>0.019554</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>0.099658</v>
+      </c>
+      <c r="F63" s="9" t="n">
+        <v>0.055976</v>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>0.015555</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>0.013731</v>
+      </c>
+      <c r="I63" s="9" t="n">
+        <v>0.049792</v>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0.023677</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>3T-07</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>39264</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <v>-0.01183</v>
+      </c>
+      <c r="D64" s="10" t="n">
+        <v>0.021719</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.159008</v>
+      </c>
+      <c r="F64" s="10" t="n">
+        <v>0.052061</v>
+      </c>
+      <c r="G64" s="10" t="n">
+        <v>0.010988</v>
+      </c>
+      <c r="H64" s="10" t="n">
+        <v>0.004328</v>
+      </c>
+      <c r="I64" s="10" t="n">
+        <v>-0.009429999999999999</v>
+      </c>
+      <c r="J64" s="10" t="n">
+        <v>0.033601</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>4T-07</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>39356</v>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>0.010627</v>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0.022039</v>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>0.280669</v>
+      </c>
+      <c r="F65" s="9" t="n">
+        <v>0.025929</v>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>-0.013661</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>0.009540999999999999</v>
+      </c>
+      <c r="I65" s="9" t="n">
+        <v>0.022439</v>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0.034609</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>1T-08</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>39448</v>
+      </c>
+      <c r="C66" s="10" t="n">
+        <v>-0.028282</v>
+      </c>
+      <c r="D66" s="10" t="n">
+        <v>0.007967999999999999</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>-0.168457</v>
+      </c>
+      <c r="F66" s="10" t="n">
+        <v>-0.015147</v>
+      </c>
+      <c r="G66" s="10" t="n">
+        <v>-0.016422</v>
+      </c>
+      <c r="H66" s="10" t="n">
+        <v>-0.003942</v>
+      </c>
+      <c r="I66" s="10" t="n">
+        <v>-0.045864</v>
+      </c>
+      <c r="J66" s="10" t="n">
+        <v>0.014464</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>2T-08</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>39539</v>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>0.055046</v>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0.023844</v>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>0.146415</v>
+      </c>
+      <c r="F67" s="9" t="n">
+        <v>0.026729</v>
+      </c>
+      <c r="G67" s="9" t="n">
+        <v>0.028455</v>
+      </c>
+      <c r="H67" s="9" t="n">
+        <v>0.008710000000000001</v>
+      </c>
+      <c r="I67" s="9" t="n">
+        <v>0.065455</v>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0.0296</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>3T-08</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>39630</v>
+      </c>
+      <c r="C68" s="10" t="n">
+        <v>-0.023937</v>
+      </c>
+      <c r="D68" s="10" t="n">
+        <v>0.011301</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.192987</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>-0.014755</v>
+      </c>
+      <c r="G68" s="10" t="n">
+        <v>-0.010111</v>
+      </c>
+      <c r="H68" s="10" t="n">
+        <v>-0.012341</v>
+      </c>
+      <c r="I68" s="10" t="n">
+        <v>-0.013772</v>
+      </c>
+      <c r="J68" s="10" t="n">
+        <v>0.025087</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>4T-08</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>39722</v>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>-0.006095</v>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>-0.005432</v>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>0.335984</v>
+      </c>
+      <c r="F69" s="9" t="n">
+        <v>0.027799</v>
+      </c>
+      <c r="G69" s="9" t="n">
+        <v>-0.02726</v>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>-0.025959</v>
+      </c>
+      <c r="I69" s="9" t="n">
+        <v>-0.00197</v>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>0.000615</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>1T-09</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>39814</v>
+      </c>
+      <c r="C70" s="10" t="n">
+        <v>-0.090015</v>
+      </c>
+      <c r="D70" s="10" t="n">
+        <v>-0.068616</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>-0.203549</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>-0.015575</v>
+      </c>
+      <c r="G70" s="10" t="n">
+        <v>-0.090655</v>
+      </c>
+      <c r="H70" s="10" t="n">
+        <v>-0.099471</v>
+      </c>
+      <c r="I70" s="10" t="n">
+        <v>-0.089682</v>
+      </c>
+      <c r="J70" s="10" t="n">
+        <v>-0.045338</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>2T-09</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>39904</v>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>0.015661</v>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>-0.103385</v>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>0.136563</v>
+      </c>
+      <c r="F71" s="9" t="n">
+        <v>-0.024035</v>
+      </c>
+      <c r="G71" s="9" t="n">
+        <v>0.005789</v>
+      </c>
+      <c r="H71" s="9" t="n">
+        <v>-0.119318</v>
+      </c>
+      <c r="I71" s="9" t="n">
+        <v>0.017072</v>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>-0.08869</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>3T-09</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>39995</v>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>0.024679</v>
+      </c>
+      <c r="D72" s="10" t="n">
+        <v>-0.058727</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.187027</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>-0.016826</v>
+      </c>
+      <c r="G72" s="10" t="n">
+        <v>0.041102</v>
+      </c>
+      <c r="H72" s="10" t="n">
+        <v>-0.073755</v>
+      </c>
+      <c r="I72" s="10" t="n">
+        <v>0.03291</v>
+      </c>
+      <c r="J72" s="10" t="n">
+        <v>-0.045555</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>4T-09</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>40087</v>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>0.034806</v>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>-0.019992</v>
+      </c>
+      <c r="E73" s="9" t="n">
+        <v>0.291689</v>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>-0.049424</v>
+      </c>
+      <c r="G73" s="9" t="n">
+        <v>0.018847</v>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>-0.029852</v>
+      </c>
+      <c r="I73" s="9" t="n">
+        <v>0.037133</v>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>-0.008159</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>1T-10</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>40179</v>
+      </c>
+      <c r="C74" s="10" t="n">
+        <v>-0.029645</v>
+      </c>
+      <c r="D74" s="10" t="n">
+        <v>0.045023</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>-0.180924</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>-0.02242</v>
+      </c>
+      <c r="G74" s="10" t="n">
+        <v>-0.016629</v>
+      </c>
+      <c r="H74" s="10" t="n">
+        <v>0.049124</v>
+      </c>
+      <c r="I74" s="10" t="n">
+        <v>-0.033975</v>
+      </c>
+      <c r="J74" s="10" t="n">
+        <v>0.052536</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>2T-10</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>40269</v>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>0.041746</v>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>0.071863</v>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>0.232729</v>
+      </c>
+      <c r="F75" s="9" t="n">
+        <v>0.060294</v>
+      </c>
+      <c r="G75" s="9" t="n">
+        <v>0.029217</v>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>0.073561</v>
+      </c>
+      <c r="I75" s="9" t="n">
+        <v>0.038601</v>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>0.07481599999999999</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>3T-10</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>40360</v>
+      </c>
+      <c r="C76" s="10" t="n">
+        <v>0.001003</v>
+      </c>
+      <c r="D76" s="10" t="n">
+        <v>0.047096</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.186346</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>0.061183</v>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>0.013187</v>
+      </c>
+      <c r="H76" s="10" t="n">
+        <v>0.044776</v>
+      </c>
+      <c r="I76" s="10" t="n">
+        <v>0.013039</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>0.054139</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>4T-10</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>40452</v>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>0.023552</v>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>0.035709</v>
+      </c>
+      <c r="E77" s="9" t="n">
+        <v>0.217548</v>
+      </c>
+      <c r="F77" s="9" t="n">
+        <v>0.000272</v>
+      </c>
+      <c r="G77" s="9" t="n">
+        <v>-0.003192</v>
+      </c>
+      <c r="H77" s="9" t="n">
+        <v>0.022175</v>
+      </c>
+      <c r="I77" s="9" t="n">
+        <v>0.036266</v>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>0.053257</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>1T-11</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>40544</v>
+      </c>
+      <c r="C78" s="10" t="n">
+        <v>-0.028304</v>
+      </c>
+      <c r="D78" s="10" t="n">
+        <v>0.037141</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>-0.174422</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>0.008212000000000001</v>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>-0.017781</v>
+      </c>
+      <c r="H78" s="10" t="n">
+        <v>0.020977</v>
+      </c>
+      <c r="I78" s="10" t="n">
+        <v>-0.035783</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>0.051285</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>2T-11</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>40634</v>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>0.029445</v>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.024894</v>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>0.08230800000000001</v>
+      </c>
+      <c r="F79" s="9" t="n">
+        <v>-0.114813</v>
+      </c>
+      <c r="G79" s="9" t="n">
+        <v>0.029788</v>
+      </c>
+      <c r="H79" s="9" t="n">
+        <v>0.021543</v>
+      </c>
+      <c r="I79" s="9" t="n">
+        <v>0.02615</v>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.038683</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>3T-11</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>40725</v>
+      </c>
+      <c r="C80" s="10" t="n">
+        <v>0.012921</v>
+      </c>
+      <c r="D80" s="10" t="n">
+        <v>0.037097</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.07843700000000001</v>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>0.002583</v>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>0.023029</v>
+      </c>
+      <c r="H80" s="10" t="n">
+        <v>0.031467</v>
+      </c>
+      <c r="I80" s="10" t="n">
+        <v>0.019875</v>
+      </c>
+      <c r="J80" s="10" t="n">
+        <v>0.045691</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>4T-11</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>40817</v>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>0.025069</v>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>0.038633</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>0.237156</v>
+      </c>
+      <c r="F81" s="9" t="n">
+        <v>0.018729</v>
+      </c>
+      <c r="G81" s="9" t="n">
+        <v>0.016023</v>
+      </c>
+      <c r="H81" s="9" t="n">
+        <v>0.051351</v>
+      </c>
+      <c r="I81" s="9" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>0.034172</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>1T-12</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>40909</v>
+      </c>
+      <c r="C82" s="10" t="n">
+        <v>-0.018235</v>
+      </c>
+      <c r="D82" s="10" t="n">
+        <v>0.049396</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>-0.15982</v>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>0.036747</v>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>-0.012429</v>
+      </c>
+      <c r="H82" s="10" t="n">
+        <v>0.057079</v>
+      </c>
+      <c r="I82" s="10" t="n">
+        <v>-0.023575</v>
+      </c>
+      <c r="J82" s="10" t="n">
+        <v>0.047265</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>2T-12</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C83" s="9" t="n">
+        <v>0.02079</v>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>0.040573</v>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>0.173007</v>
+      </c>
+      <c r="F83" s="9" t="n">
+        <v>0.123629</v>
+      </c>
+      <c r="G83" s="9" t="n">
+        <v>0.018356</v>
+      </c>
+      <c r="H83" s="9" t="n">
+        <v>0.045345</v>
+      </c>
+      <c r="I83" s="9" t="n">
+        <v>0.015462</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>0.036357</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>3T-12</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>41091</v>
+      </c>
+      <c r="C84" s="10" t="n">
+        <v>-0.002003</v>
+      </c>
+      <c r="D84" s="10" t="n">
+        <v>0.025242</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>-0.175623</v>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>0.005133</v>
+      </c>
+      <c r="G84" s="10" t="n">
+        <v>0.013641</v>
+      </c>
+      <c r="H84" s="10" t="n">
+        <v>0.035752</v>
+      </c>
+      <c r="I84" s="10" t="n">
+        <v>0.004724</v>
+      </c>
+      <c r="J84" s="10" t="n">
+        <v>0.020961</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>4T-12</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>41183</v>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>0.027571</v>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>0.027745</v>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="F85" s="9" t="n">
+        <v>0.069287</v>
+      </c>
+      <c r="G85" s="9" t="n">
+        <v>-0.012878</v>
+      </c>
+      <c r="H85" s="9" t="n">
+        <v>0.00629</v>
+      </c>
+      <c r="I85" s="9" t="n">
+        <v>0.04445</v>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>0.040488</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>1T-13</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>41275</v>
+      </c>
+      <c r="C86" s="10" t="n">
+        <v>-0.047365</v>
+      </c>
+      <c r="D86" s="10" t="n">
+        <v>-0.00275</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>-0.205433</v>
+      </c>
+      <c r="F86" s="10" t="n">
+        <v>0.011235</v>
+      </c>
+      <c r="G86" s="10" t="n">
+        <v>-0.035551</v>
+      </c>
+      <c r="H86" s="10" t="n">
+        <v>-0.01727</v>
+      </c>
+      <c r="I86" s="10" t="n">
+        <v>-0.054781</v>
+      </c>
+      <c r="J86" s="10" t="n">
+        <v>0.007235</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>2T-13</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>41365</v>
+      </c>
+      <c r="C87" s="9" t="n">
+        <v>0.041269</v>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>0.017256</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>0.213202</v>
+      </c>
+      <c r="F87" s="9" t="n">
+        <v>0.045887</v>
+      </c>
+      <c r="G87" s="9" t="n">
+        <v>0.037141</v>
+      </c>
+      <c r="H87" s="9" t="n">
+        <v>0.000857</v>
+      </c>
+      <c r="I87" s="9" t="n">
+        <v>0.035531</v>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>0.027142</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>3T-13</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>41456</v>
+      </c>
+      <c r="C88" s="10" t="n">
+        <v>-0.008710000000000001</v>
+      </c>
+      <c r="D88" s="10" t="n">
+        <v>0.01042</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>-0.187264</v>
+      </c>
+      <c r="F88" s="10" t="n">
+        <v>0.031118</v>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>0.00193</v>
+      </c>
+      <c r="H88" s="10" t="n">
+        <v>-0.010707</v>
+      </c>
+      <c r="I88" s="10" t="n">
+        <v>0.001145</v>
+      </c>
+      <c r="J88" s="10" t="n">
+        <v>0.023482</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>4T-13</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>41548</v>
+      </c>
+      <c r="C89" s="9" t="n">
+        <v>0.026047</v>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>0.008921999999999999</v>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>0.314409</v>
+      </c>
+      <c r="F89" s="9" t="n">
+        <v>0.029778</v>
+      </c>
+      <c r="G89" s="9" t="n">
+        <v>0.00369</v>
+      </c>
+      <c r="H89" s="9" t="n">
+        <v>0.005898</v>
+      </c>
+      <c r="I89" s="9" t="n">
+        <v>0.031469</v>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>0.010762</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>1T-14</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>41640</v>
+      </c>
+      <c r="C90" s="10" t="n">
+        <v>-0.032348</v>
+      </c>
+      <c r="D90" s="10" t="n">
+        <v>0.024826</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>-0.193073</v>
+      </c>
+      <c r="F90" s="10" t="n">
+        <v>0.045798</v>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>-0.016323</v>
+      </c>
+      <c r="H90" s="10" t="n">
+        <v>0.025952</v>
+      </c>
+      <c r="I90" s="10" t="n">
+        <v>-0.043321</v>
+      </c>
+      <c r="J90" s="10" t="n">
+        <v>0.023017</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>2T-14</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>41730</v>
+      </c>
+      <c r="C91" s="9" t="n">
+        <v>0.035845</v>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>0.019487</v>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>0.18553</v>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>0.021944</v>
+      </c>
+      <c r="G91" s="9" t="n">
+        <v>0.038668</v>
+      </c>
+      <c r="H91" s="9" t="n">
+        <v>0.027463</v>
+      </c>
+      <c r="I91" s="9" t="n">
+        <v>0.027551</v>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>0.015133</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>3T-14</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>41821</v>
+      </c>
+      <c r="C92" s="10" t="n">
+        <v>-0.002776</v>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>0.02559</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>-0.163095</v>
+      </c>
+      <c r="F92" s="10" t="n">
+        <v>0.052334</v>
+      </c>
+      <c r="G92" s="10" t="n">
+        <v>0.003261</v>
+      </c>
+      <c r="H92" s="10" t="n">
+        <v>0.028829</v>
+      </c>
+      <c r="I92" s="10" t="n">
+        <v>0.009306</v>
+      </c>
+      <c r="J92" s="10" t="n">
+        <v>0.023408</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>4T-14</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>41913</v>
+      </c>
+      <c r="C93" s="9" t="n">
+        <v>0.030616</v>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>0.030156</v>
+      </c>
+      <c r="E93" s="9" t="n">
+        <v>0.266211</v>
+      </c>
+      <c r="F93" s="9" t="n">
+        <v>0.013746</v>
+      </c>
+      <c r="G93" s="9" t="n">
+        <v>0.008617</v>
+      </c>
+      <c r="H93" s="9" t="n">
+        <v>0.033879</v>
+      </c>
+      <c r="I93" s="9" t="n">
+        <v>0.035887</v>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>0.027791</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>1T-15</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>42005</v>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>-0.03357</v>
+      </c>
+      <c r="D94" s="10" t="n">
+        <v>0.028855</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.16182</v>
+      </c>
+      <c r="F94" s="10" t="n">
+        <v>0.053008</v>
+      </c>
+      <c r="G94" s="10" t="n">
+        <v>-0.029035</v>
+      </c>
+      <c r="H94" s="10" t="n">
+        <v>0.020518</v>
+      </c>
+      <c r="I94" s="10" t="n">
+        <v>-0.039316</v>
+      </c>
+      <c r="J94" s="10" t="n">
+        <v>0.032093</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>2T-15</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>42095</v>
+      </c>
+      <c r="C95" s="9" t="n">
+        <v>0.030378</v>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>0.023426</v>
+      </c>
+      <c r="E95" s="9" t="n">
+        <v>0.116571</v>
+      </c>
+      <c r="F95" s="9" t="n">
+        <v>-0.008241999999999999</v>
+      </c>
+      <c r="G95" s="9" t="n">
+        <v>0.024683</v>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>0.006777</v>
+      </c>
+      <c r="I95" s="9" t="n">
+        <v>0.028334</v>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>0.03288</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>3T-15</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>42186</v>
+      </c>
+      <c r="C96" s="10" t="n">
+        <v>0.007386</v>
+      </c>
+      <c r="D96" s="10" t="n">
+        <v>0.033855</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>-0.16844</v>
+      </c>
+      <c r="F96" s="10" t="n">
+        <v>-0.014576</v>
+      </c>
+      <c r="G96" s="10" t="n">
+        <v>0.030391</v>
+      </c>
+      <c r="H96" s="10" t="n">
+        <v>0.034002</v>
+      </c>
+      <c r="I96" s="10" t="n">
+        <v>0.009775000000000001</v>
+      </c>
+      <c r="J96" s="10" t="n">
+        <v>0.03336</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>4T-15</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>42278</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>0.018971</v>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>0.022174</v>
+      </c>
+      <c r="E97" s="9" t="n">
+        <v>0.339539</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>0.042492</v>
+      </c>
+      <c r="G97" s="9" t="n">
+        <v>-0.013207</v>
+      </c>
+      <c r="H97" s="9" t="n">
+        <v>0.011629</v>
+      </c>
+      <c r="I97" s="9" t="n">
+        <v>0.02558</v>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>0.023078</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>1T-16</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>42370</v>
+      </c>
+      <c r="C98" s="10" t="n">
+        <v>-0.038863</v>
+      </c>
+      <c r="D98" s="10" t="n">
+        <v>0.016576</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>-0.204531</v>
+      </c>
+      <c r="F98" s="10" t="n">
+        <v>-0.010631</v>
+      </c>
+      <c r="G98" s="10" t="n">
+        <v>-0.029559</v>
+      </c>
+      <c r="H98" s="10" t="n">
+        <v>0.011083</v>
+      </c>
+      <c r="I98" s="10" t="n">
+        <v>-0.041898</v>
+      </c>
+      <c r="J98" s="10" t="n">
+        <v>0.020329</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>2T-16</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>42461</v>
+      </c>
+      <c r="C99" s="9" t="n">
+        <v>0.036514</v>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>0.02263</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>0.15966</v>
+      </c>
+      <c r="F99" s="9" t="n">
+        <v>0.027549</v>
+      </c>
+      <c r="G99" s="9" t="n">
+        <v>0.029577</v>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>0.015913</v>
+      </c>
+      <c r="I99" s="9" t="n">
+        <v>0.034077</v>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>0.026026</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>3T-16</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="n">
+        <v>42552</v>
+      </c>
+      <c r="C100" s="10" t="n">
+        <v>-0.006225</v>
+      </c>
+      <c r="D100" s="10" t="n">
+        <v>0.008813</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.138225</v>
+      </c>
+      <c r="F100" s="10" t="n">
+        <v>0.064885</v>
+      </c>
+      <c r="G100" s="10" t="n">
+        <v>-0.000647</v>
+      </c>
+      <c r="H100" s="10" t="n">
+        <v>-0.014689</v>
+      </c>
+      <c r="I100" s="10" t="n">
+        <v>0.002659</v>
+      </c>
+      <c r="J100" s="10" t="n">
+        <v>0.018796</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>4T-16</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>42644</v>
+      </c>
+      <c r="C101" s="9" t="n">
+        <v>0.033078</v>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>0.022779</v>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>0.303088</v>
+      </c>
+      <c r="F101" s="9" t="n">
+        <v>0.035908</v>
+      </c>
+      <c r="G101" s="9" t="n">
+        <v>0.001404</v>
+      </c>
+      <c r="H101" s="9" t="n">
+        <v>-0.0001</v>
+      </c>
+      <c r="I101" s="9" t="n">
+        <v>0.042333</v>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>0.035438</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>1T-17</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="n">
+        <v>42736</v>
+      </c>
+      <c r="C102" s="10" t="n">
+        <v>-0.028203</v>
+      </c>
+      <c r="D102" s="10" t="n">
+        <v>0.034123</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>-0.188388</v>
+      </c>
+      <c r="F102" s="10" t="n">
+        <v>0.056931</v>
+      </c>
+      <c r="G102" s="10" t="n">
+        <v>-0.006544</v>
+      </c>
+      <c r="H102" s="10" t="n">
+        <v>0.023613</v>
+      </c>
+      <c r="I102" s="10" t="n">
+        <v>-0.038906</v>
+      </c>
+      <c r="J102" s="10" t="n">
+        <v>0.038671</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2T-17</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>42826</v>
+      </c>
+      <c r="C103" s="9" t="n">
+        <v>0.017346</v>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>0.014999</v>
+      </c>
+      <c r="E103" s="9" t="n">
+        <v>0.126431</v>
+      </c>
+      <c r="F103" s="9" t="n">
+        <v>0.026646</v>
+      </c>
+      <c r="G103" s="9" t="n">
+        <v>0.005029</v>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>-0.000792</v>
+      </c>
+      <c r="I103" s="9" t="n">
+        <v>0.017595</v>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>0.022117</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>3T-17</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>42917</v>
+      </c>
+      <c r="C104" s="10" t="n">
+        <v>-0.009239000000000001</v>
+      </c>
+      <c r="D104" s="10" t="n">
+        <v>0.01192</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.158121</v>
+      </c>
+      <c r="F104" s="10" t="n">
+        <v>0.002944</v>
+      </c>
+      <c r="G104" s="10" t="n">
+        <v>0.003528</v>
+      </c>
+      <c r="H104" s="10" t="n">
+        <v>0.003382</v>
+      </c>
+      <c r="I104" s="10" t="n">
+        <v>-0.00204</v>
+      </c>
+      <c r="J104" s="10" t="n">
+        <v>0.017327</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>4T-17</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="n">
+        <v>43009</v>
+      </c>
+      <c r="C105" s="9" t="n">
+        <v>0.035652</v>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>0.014441</v>
+      </c>
+      <c r="E105" s="9" t="n">
+        <v>0.354147</v>
+      </c>
+      <c r="F105" s="9" t="n">
+        <v>0.042243</v>
+      </c>
+      <c r="G105" s="9" t="n">
+        <v>-0.002626</v>
+      </c>
+      <c r="H105" s="9" t="n">
+        <v>-0.000656</v>
+      </c>
+      <c r="I105" s="9" t="n">
+        <v>0.047289</v>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>0.022164</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>1T-18</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="n">
+        <v>43101</v>
+      </c>
+      <c r="C106" s="10" t="n">
+        <v>-0.031254</v>
+      </c>
+      <c r="D106" s="10" t="n">
+        <v>0.011256</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>-0.186015</v>
+      </c>
+      <c r="F106" s="10" t="n">
+        <v>0.04529</v>
+      </c>
+      <c r="G106" s="10" t="n">
+        <v>-0.018908</v>
+      </c>
+      <c r="H106" s="10" t="n">
+        <v>-0.013093</v>
+      </c>
+      <c r="I106" s="10" t="n">
+        <v>-0.038714</v>
+      </c>
+      <c r="J106" s="10" t="n">
+        <v>0.022369</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2T-18</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="n">
+        <v>43191</v>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>0.035104</v>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>0.028908</v>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>0.12046</v>
+      </c>
+      <c r="F107" s="9" t="n">
+        <v>0.039749</v>
+      </c>
+      <c r="G107" s="9" t="n">
+        <v>0.032998</v>
+      </c>
+      <c r="H107" s="9" t="n">
+        <v>0.014371</v>
+      </c>
+      <c r="I107" s="9" t="n">
+        <v>0.032441</v>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>0.037285</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>3T-18</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>43282</v>
+      </c>
+      <c r="C108" s="10" t="n">
+        <v>-0.010594</v>
+      </c>
+      <c r="D108" s="10" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.18831</v>
+      </c>
+      <c r="F108" s="10" t="n">
+        <v>0.002465</v>
+      </c>
+      <c r="G108" s="10" t="n">
+        <v>0.002516</v>
+      </c>
+      <c r="H108" s="10" t="n">
+        <v>0.013349</v>
+      </c>
+      <c r="I108" s="10" t="n">
+        <v>-0.002588</v>
+      </c>
+      <c r="J108" s="10" t="n">
+        <v>0.036715</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>4T-18</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>43374</v>
+      </c>
+      <c r="C109" s="9" t="n">
+        <v>0.019388</v>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>0.011365</v>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>0.366384</v>
+      </c>
+      <c r="F109" s="9" t="n">
+        <v>0.011524</v>
+      </c>
+      <c r="G109" s="9" t="n">
+        <v>-0.023746</v>
+      </c>
+      <c r="H109" s="9" t="n">
+        <v>-0.008109999999999999</v>
+      </c>
+      <c r="I109" s="9" t="n">
+        <v>0.030707</v>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>0.020301</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>1T-19</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="n">
+        <v>43466</v>
+      </c>
+      <c r="C110" s="10" t="n">
+        <v>-0.03311</v>
+      </c>
+      <c r="D110" s="10" t="n">
+        <v>0.009427</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>-0.177904</v>
+      </c>
+      <c r="F110" s="10" t="n">
+        <v>0.021603</v>
+      </c>
+      <c r="G110" s="10" t="n">
+        <v>-0.012283</v>
+      </c>
+      <c r="H110" s="10" t="n">
+        <v>-0.001412</v>
+      </c>
+      <c r="I110" s="10" t="n">
+        <v>-0.044346</v>
+      </c>
+      <c r="J110" s="10" t="n">
+        <v>0.014323</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2T-19</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="n">
+        <v>43556</v>
+      </c>
+      <c r="C111" s="9" t="n">
+        <v>0.015309</v>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>-0.009875999999999999</v>
+      </c>
+      <c r="E111" s="9" t="n">
+        <v>0.090306</v>
+      </c>
+      <c r="F111" s="9" t="n">
+        <v>-0.005891</v>
+      </c>
+      <c r="G111" s="9" t="n">
+        <v>0.013793</v>
+      </c>
+      <c r="H111" s="9" t="n">
+        <v>-0.019978</v>
+      </c>
+      <c r="I111" s="9" t="n">
+        <v>0.012197</v>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>-0.005566</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>3T-19</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="n">
+        <v>43647</v>
+      </c>
+      <c r="C112" s="10" t="n">
+        <v>-0.005377</v>
+      </c>
+      <c r="D112" s="10" t="n">
+        <v>-0.004656</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.168809</v>
+      </c>
+      <c r="F112" s="10" t="n">
+        <v>0.017992</v>
+      </c>
+      <c r="G112" s="10" t="n">
+        <v>0.005129</v>
+      </c>
+      <c r="H112" s="10" t="n">
+        <v>-0.017424</v>
+      </c>
+      <c r="I112" s="10" t="n">
+        <v>0.003583</v>
+      </c>
+      <c r="J112" s="10" t="n">
+        <v>0.000586</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>4T-19</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="n">
+        <v>43739</v>
+      </c>
+      <c r="C113" s="9" t="n">
+        <v>0.013808</v>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>-0.010104</v>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>0.322148</v>
+      </c>
+      <c r="F113" s="9" t="n">
+        <v>-0.014966</v>
+      </c>
+      <c r="G113" s="9" t="n">
+        <v>-0.036834</v>
+      </c>
+      <c r="H113" s="9" t="n">
+        <v>-0.030597</v>
+      </c>
+      <c r="I113" s="9" t="n">
+        <v>0.030212</v>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>0.000105</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>1T-20</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C114" s="10" t="n">
+        <v>-0.037224</v>
+      </c>
+      <c r="D114" s="10" t="n">
+        <v>-0.014316</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>-0.17499</v>
+      </c>
+      <c r="F114" s="10" t="n">
+        <v>-0.011474</v>
+      </c>
+      <c r="G114" s="10" t="n">
+        <v>-0.00751</v>
+      </c>
+      <c r="H114" s="10" t="n">
+        <v>-0.025912</v>
+      </c>
+      <c r="I114" s="10" t="n">
+        <v>-0.050272</v>
+      </c>
+      <c r="J114" s="10" t="n">
+        <v>-0.006097</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2T-20</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="n">
+        <v>43922</v>
+      </c>
+      <c r="C115" s="9" t="n">
+        <v>-0.178987</v>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>-0.202943</v>
+      </c>
+      <c r="E115" s="9" t="n">
+        <v>0.08963699999999999</v>
+      </c>
+      <c r="F115" s="9" t="n">
+        <v>-0.01208</v>
+      </c>
+      <c r="G115" s="9" t="n">
+        <v>-0.213012</v>
+      </c>
+      <c r="H115" s="9" t="n">
+        <v>-0.243834</v>
+      </c>
+      <c r="I115" s="9" t="n">
+        <v>-0.167626</v>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>-0.182669</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>3T-20</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="n">
+        <v>44013</v>
+      </c>
+      <c r="C116" s="10" t="n">
+        <v>0.146445</v>
+      </c>
+      <c r="D116" s="10" t="n">
+        <v>-0.081278</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.11029</v>
+      </c>
+      <c r="F116" s="10" t="n">
+        <v>0.057473</v>
+      </c>
+      <c r="G116" s="10" t="n">
+        <v>0.232939</v>
+      </c>
+      <c r="H116" s="10" t="n">
+        <v>-0.072451</v>
+      </c>
+      <c r="I116" s="10" t="n">
+        <v>0.119236</v>
+      </c>
+      <c r="J116" s="10" t="n">
+        <v>-0.08848</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>4T-20</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>44105</v>
+      </c>
+      <c r="C117" s="9" t="n">
+        <v>0.064905</v>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>-0.034974</v>
+      </c>
+      <c r="E117" s="9" t="n">
+        <v>0.270674</v>
+      </c>
+      <c r="F117" s="9" t="n">
+        <v>0.016304</v>
+      </c>
+      <c r="G117" s="9" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="H117" s="9" t="n">
+        <v>-0.007992000000000001</v>
+      </c>
+      <c r="I117" s="9" t="n">
+        <v>0.07606</v>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>-0.047914</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>1T-21</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="n">
+        <v>44197</v>
+      </c>
+      <c r="C118" s="10" t="n">
+        <v>-0.028226</v>
+      </c>
+      <c r="D118" s="10" t="n">
+        <v>-0.025955</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>-0.183706</v>
+      </c>
+      <c r="F118" s="10" t="n">
+        <v>0.005567</v>
+      </c>
+      <c r="G118" s="10" t="n">
+        <v>-0.016106</v>
+      </c>
+      <c r="H118" s="10" t="n">
+        <v>-0.016584</v>
+      </c>
+      <c r="I118" s="10" t="n">
+        <v>-0.031234</v>
+      </c>
+      <c r="J118" s="10" t="n">
+        <v>-0.028829</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2T-21</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="n">
+        <v>44287</v>
+      </c>
+      <c r="C119" s="9" t="n">
+        <v>0.03424</v>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>0.227018</v>
+      </c>
+      <c r="E119" s="9" t="n">
+        <v>0.150847</v>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>0.062054</v>
+      </c>
+      <c r="G119" s="9" t="n">
+        <v>0.018039</v>
+      </c>
+      <c r="H119" s="9" t="n">
+        <v>0.272136</v>
+      </c>
+      <c r="I119" s="9" t="n">
+        <v>0.033373</v>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>0.205685</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>3T-21</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>44378</v>
+      </c>
+      <c r="C120" s="10" t="n">
+        <v>-0.017722</v>
+      </c>
+      <c r="D120" s="10" t="n">
+        <v>0.051313</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>-0.173905</v>
+      </c>
+      <c r="F120" s="10" t="n">
+        <v>-0.013883</v>
+      </c>
+      <c r="G120" s="10" t="n">
+        <v>0.002805</v>
+      </c>
+      <c r="H120" s="10" t="n">
+        <v>0.034685</v>
+      </c>
+      <c r="I120" s="10" t="n">
+        <v>-0.01798</v>
+      </c>
+      <c r="J120" s="10" t="n">
+        <v>0.057871</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>4T-21</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="n">
+        <v>44470</v>
+      </c>
+      <c r="C121" s="9" t="n">
+        <v>0.032102</v>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>0.018929</v>
+      </c>
+      <c r="E121" s="9" t="n">
+        <v>0.330352</v>
+      </c>
+      <c r="F121" s="9" t="n">
+        <v>0.032431</v>
+      </c>
+      <c r="G121" s="9" t="n">
+        <v>0.003983</v>
+      </c>
+      <c r="H121" s="9" t="n">
+        <v>0.008451999999999999</v>
+      </c>
+      <c r="I121" s="9" t="n">
+        <v>0.033862</v>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>0.016387</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>1T-22</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="n">
+        <v>44562</v>
+      </c>
+      <c r="C122" s="10" t="n">
+        <v>-0.021259</v>
+      </c>
+      <c r="D122" s="10" t="n">
+        <v>0.026234</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.203606</v>
+      </c>
+      <c r="F122" s="10" t="n">
+        <v>0.007262</v>
+      </c>
+      <c r="G122" s="10" t="n">
+        <v>0.016633</v>
+      </c>
+      <c r="H122" s="10" t="n">
+        <v>0.042009</v>
+      </c>
+      <c r="I122" s="10" t="n">
+        <v>-0.03225</v>
+      </c>
+      <c r="J122" s="10" t="n">
+        <v>0.01532</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>2T-22</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="n">
+        <v>44652</v>
+      </c>
+      <c r="C123" s="9" t="n">
+        <v>0.037092</v>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>0.029063</v>
+      </c>
+      <c r="E123" s="9" t="n">
+        <v>0.138945</v>
+      </c>
+      <c r="F123" s="9" t="n">
+        <v>-0.003155</v>
+      </c>
+      <c r="G123" s="9" t="n">
+        <v>0.020755</v>
+      </c>
+      <c r="H123" s="9" t="n">
+        <v>0.044789</v>
+      </c>
+      <c r="I123" s="9" t="n">
+        <v>0.036781</v>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0.018669</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>3T-22</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="n">
+        <v>44743</v>
+      </c>
+      <c r="C124" s="10" t="n">
+        <v>-0.000849</v>
+      </c>
+      <c r="D124" s="10" t="n">
+        <v>0.04674</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.165736</v>
+      </c>
+      <c r="F124" s="10" t="n">
+        <v>0.006703</v>
+      </c>
+      <c r="G124" s="10" t="n">
+        <v>0.010005</v>
+      </c>
+      <c r="H124" s="10" t="n">
+        <v>0.052291</v>
+      </c>
+      <c r="I124" s="10" t="n">
+        <v>0.006708</v>
+      </c>
+      <c r="J124" s="10" t="n">
+        <v>0.044279</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>4T-22</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="n">
+        <v>44835</v>
+      </c>
+      <c r="C125" s="9" t="n">
+        <v>0.031414</v>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>0.046042</v>
+      </c>
+      <c r="E125" s="9" t="n">
+        <v>0.382477</v>
+      </c>
+      <c r="F125" s="9" t="n">
+        <v>0.046146</v>
+      </c>
+      <c r="G125" s="9" t="n">
+        <v>0.002705</v>
+      </c>
+      <c r="H125" s="9" t="n">
+        <v>0.050951</v>
+      </c>
+      <c r="I125" s="9" t="n">
+        <v>0.033149</v>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>0.043559</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>1T-23</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="n">
+        <v>44927</v>
+      </c>
+      <c r="C126" s="10" t="n">
+        <v>-0.028796</v>
+      </c>
+      <c r="D126" s="10" t="n">
+        <v>0.037986</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.234336</v>
+      </c>
+      <c r="F126" s="10" t="n">
+        <v>0.005779</v>
+      </c>
+      <c r="G126" s="10" t="n">
+        <v>-0.003403</v>
+      </c>
+      <c r="H126" s="10" t="n">
+        <v>0.030238</v>
+      </c>
+      <c r="I126" s="10" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="J126" s="10" t="n">
+        <v>0.040917</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>2T-23</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>45017</v>
+      </c>
+      <c r="C127" s="9" t="n">
+        <v>0.031946</v>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>0.032836</v>
+      </c>
+      <c r="E127" s="9" t="n">
+        <v>0.128521</v>
+      </c>
+      <c r="F127" s="9" t="n">
+        <v>-0.003427</v>
+      </c>
+      <c r="G127" s="9" t="n">
+        <v>0.021028</v>
+      </c>
+      <c r="H127" s="9" t="n">
+        <v>0.030514</v>
+      </c>
+      <c r="I127" s="9" t="n">
+        <v>0.031359</v>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>0.035474</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>3T-23</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>45108</v>
+      </c>
+      <c r="C128" s="10" t="n">
+        <v>-0.000537</v>
+      </c>
+      <c r="D128" s="10" t="n">
+        <v>0.033159</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>-0.15719</v>
+      </c>
+      <c r="F128" s="10" t="n">
+        <v>0.006782</v>
+      </c>
+      <c r="G128" s="10" t="n">
+        <v>0.012154</v>
+      </c>
+      <c r="H128" s="10" t="n">
+        <v>0.032706</v>
+      </c>
+      <c r="I128" s="10" t="n">
+        <v>0.006101</v>
+      </c>
+      <c r="J128" s="10" t="n">
+        <v>0.034849</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>4T-23</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="n">
+        <v>45200</v>
+      </c>
+      <c r="C129" s="9" t="n">
+        <v>0.019737</v>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>0.021462</v>
+      </c>
+      <c r="E129" s="9" t="n">
+        <v>0.313216</v>
+      </c>
+      <c r="F129" s="9" t="n">
+        <v>-0.043657</v>
+      </c>
+      <c r="G129" s="9" t="n">
+        <v>-0.004585</v>
+      </c>
+      <c r="H129" s="9" t="n">
+        <v>0.025198</v>
+      </c>
+      <c r="I129" s="9" t="n">
+        <v>0.021943</v>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>0.023624</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>1T-24</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="n">
+        <v>45292</v>
+      </c>
+      <c r="C130" s="10" t="n">
+        <v>-0.032373</v>
+      </c>
+      <c r="D130" s="10" t="n">
+        <v>0.017701</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>-0.203954</v>
+      </c>
+      <c r="F130" s="10" t="n">
+        <v>-0.005709</v>
+      </c>
+      <c r="G130" s="10" t="n">
+        <v>-0.028442</v>
+      </c>
+      <c r="H130" s="10" t="n">
+        <v>-0.00056</v>
+      </c>
+      <c r="I130" s="10" t="n">
+        <v>-0.030097</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>0.028504</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>2T-24</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>45383</v>
+      </c>
+      <c r="C131" s="9" t="n">
+        <v>0.036097</v>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>0.021794</v>
+      </c>
+      <c r="E131" s="9" t="n">
+        <v>0.135785</v>
+      </c>
+      <c r="F131" s="9" t="n">
+        <v>0.000692</v>
+      </c>
+      <c r="G131" s="9" t="n">
+        <v>0.027603</v>
+      </c>
+      <c r="H131" s="9" t="n">
+        <v>0.005877</v>
+      </c>
+      <c r="I131" s="9" t="n">
+        <v>0.034138</v>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>0.031275</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>3T-24</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>45474</v>
+      </c>
+      <c r="C132" s="10" t="n">
+        <v>-0.007017</v>
+      </c>
+      <c r="D132" s="10" t="n">
+        <v>0.015169</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>-0.096136</v>
+      </c>
+      <c r="F132" s="10" t="n">
+        <v>0.073182</v>
+      </c>
+      <c r="G132" s="10" t="n">
+        <v>0.001214</v>
+      </c>
+      <c r="H132" s="10" t="n">
+        <v>-0.004995</v>
+      </c>
+      <c r="I132" s="10" t="n">
+        <v>-0.001649</v>
+      </c>
+      <c r="J132" s="10" t="n">
+        <v>0.023332</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>4T-24</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="n">
+        <v>45566</v>
+      </c>
+      <c r="C133" s="9" t="n">
+        <v>0.008551</v>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>0.004033</v>
+      </c>
+      <c r="E133" s="9" t="n">
+        <v>-0.08500000000000001</v>
+      </c>
+      <c r="F133" s="9" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="G133" s="9" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="H133" s="9" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I133" s="9" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>1T-25</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="n">
+        <v>45658</v>
+      </c>
+      <c r="C134" s="10" t="n">
+        <v>-0.030346</v>
+      </c>
+      <c r="D134" s="10" t="n">
+        <v>0.006137</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="F134" s="10" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="G134" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H134" s="10" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="I134" s="10" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="J134" s="10" t="n">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>2T-25</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="n">
+        <v>45748</v>
+      </c>
+      <c r="C135" s="9" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="E135" s="9" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="F135" s="9" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="G135" s="9" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H135" s="9" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I135" s="9" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>0.018</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>3T-25</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="n">
+        <v>45839</v>
+      </c>
+      <c r="C136" s="10" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="D136" s="10" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F136" s="10" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="G136" s="10" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="H136" s="10" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="I136" s="10" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J136" s="10" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>4T-25</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="n">
+        <v>45931</v>
+      </c>
+      <c r="C137" s="9" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E137" s="9" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="F137" s="9" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="G137" s="9" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H137" s="9" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="I137" s="9" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>0.021</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
           <t>1T-26</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B138" s="5" t="n">
         <v>46023</v>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C138" s="10" t="n">
         <v>-0.006</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D138" s="10" t="n">
         <v>0.004</v>
       </c>
-      <c r="E28" s="10" t="n">
+      <c r="E138" s="10" t="n">
         <v>-0.017</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F138" s="10" t="n">
         <v>0.003</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G138" s="10" t="n">
         <v>-0.01</v>
       </c>
-      <c r="H28" s="10" t="n">
+      <c r="H138" s="10" t="n">
         <v>-0.011</v>
       </c>
-      <c r="I28" s="10" t="n">
+      <c r="I138" s="10" t="n">
         <v>-0.004</v>
       </c>
-      <c r="J28" s="10" t="n">
+      <c r="J138" s="10" t="n">
         <v>0.011</v>
       </c>
     </row>

--- a/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
+++ b/downloads/indicadores/PIBSEC/PIBSEC_datos.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -498,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Trimestral · Unidad: millones de pesos a precios de 2018 · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf · Fecha de publicación: 22 de mayo de 2026</t>
+          <t>Fuente: INEGI · Frecuencia: Trimestral · Unidad: millones de pesos a precios de 2018 · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_08.pdf · Fecha de publicación: 24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3458,13 +3458,33 @@
         <v>24.973976071</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>0.797675498</v>
+        <v>0.788493942</v>
       </c>
       <c r="E138" s="6" t="n">
-        <v>7.621773386</v>
+        <v>7.632084217</v>
       </c>
       <c r="F138" s="6" t="n">
-        <v>15.134329955</v>
+        <v>15.120485521</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2T-26</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="7" t="n">
+        <v>0.898248914</v>
+      </c>
+      <c r="E139" s="7" t="n">
+        <v>7.978687666</v>
+      </c>
+      <c r="F139" s="7" t="n">
+        <v>15.749814826</v>
       </c>
     </row>
   </sheetData>
@@ -3483,7 +3503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3508,7 +3528,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Trimestral · Unidad: millones de pesos a precios de 2018 · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_05.pdf · Fecha de publicación: 22 de mayo de 2026</t>
+          <t>Fuente: INEGI · Frecuencia: Trimestral · Unidad: millones de pesos a precios de 2018 · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/pibt/pib_Pconst2026_08.pdf · Fecha de publicación: 24 de agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -8051,6 +8071,40 @@
       </c>
       <c r="J138" s="10" t="n">
         <v>0.011</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>2T-26</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="C139" s="9" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="E139" s="9" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="F139" s="9" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="G139" s="9" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H139" s="9" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I139" s="9" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>0.023</v>
       </c>
     </row>
   </sheetData>
